--- a/reports/CEP_Memory_Report.xlsx
+++ b/reports/CEP_Memory_Report.xlsx
@@ -446,16 +446,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CEP01F0HPICB1R01U07.CC02.RH.RJT.GJ</t>
+          <t>CEP02F0HPICB1R02U07.CC02.RH.RJT.GJ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>87.18000000000001</v>
+        <v>87.17</v>
       </c>
     </row>
     <row r="3">
@@ -471,11 +471,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>86.84999999999999</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -486,16 +486,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CEP02F0HPICB1R02U07.CC02.RH.RJT.GJ</t>
+          <t>CEP01F0HPICB1R01U07.CC02.RH.RJT.GJ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86.62</v>
+        <v>87.08</v>
       </c>
     </row>
     <row r="5">
@@ -511,11 +511,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.66</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -531,11 +531,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73.98</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="7">
@@ -551,11 +551,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>73.69</v>
+        <v>73.76000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -571,11 +571,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73.08</v>
+        <v>73.29000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -591,11 +591,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72.87</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -611,11 +611,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.65000000000001</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="11">
@@ -626,56 +626,56 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CEP01F1HPICS1R01U05.CC03.RH.VIJ.AP</t>
+          <t>CEP02F1HPICS1R02U05.CC03.RH.VIJ.AP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72.63</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud,CC01.RH.RPT.BH</t>
+          <t>Cloud,CC03.RH.VIJ.AP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CEP01F1DECLB1R01U06.CC01.RH.RPT.BH</t>
+          <t>CEP01F1HPICS1R01U05.CC03.RH.VIJ.AP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72.56999999999999</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud,CC03.RH.VIJ.AP</t>
+          <t>Cloud,CC01.RH.RPT.BH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CEP02F1HPICS1R02U05.CC03.RH.VIJ.AP</t>
+          <t>CEP01F1DECLB1R01U06.CC01.RH.RPT.BH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>72.48</v>
+        <v>72.22</v>
       </c>
     </row>
     <row r="14">
@@ -691,11 +691,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="15">
@@ -711,11 +711,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71.13</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="16">
@@ -731,11 +731,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70.94</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -751,11 +751,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8/06/26</t>
+          <t>13-Jun-2026</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70.92</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
   </sheetData>
